--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_lstm_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_lstm_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>0.7090015670332926</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>0.3840428795918789</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,15 +999,15 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,27 +1096,27 @@
         <v>0.5706975674951219</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,27 +1124,27 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>0.6183294970973855</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>0.3750891349489416</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,31 +1287,31 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1393,27 +1394,27 @@
         <v>0.8094258395425826</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>0.7319258903805497</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,19 +1565,19 @@
         <v>0.2640193530752979</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,31 +1585,31 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1691,19 +1692,19 @@
         <v>0.754963221438956</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,27 +1720,27 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,27 +1833,27 @@
         <v>0.6779457199473258</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,19 +1863,19 @@
         <v>0.1800515930264219</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,31 +1883,31 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766684</v>
+        <v>0.05644008609220896</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208207</v>
+        <v>0.08831268540851259</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571159</v>
+        <v>0.2970580221997939</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798217</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278889</v>
+        <v>0.2724034021441999</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668931</v>
+        <v>-0.08310591627223018</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.02359204792244729</v>
+        <v>0.0817485147145196</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.07703707946457228</v>
+        <v>0.02395633122549046</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2543247912284557</v>
+        <v>0.0906505688722604</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1824361712833101</v>
+        <v>0.3208155612581201</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4816886905342951</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.0212067550577778</v>
+        <v>-0.005946824936880146</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.023869993883996</v>
+        <v>1.029090423147515</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.8838252884816873</v>
+        <v>0.3106799034324066</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1003724075845553</v>
+        <v>0.03008204884056798</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.241347098573505</v>
+        <v>1.140514035386183</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1388121261286483</v>
+        <v>-0.1021137573160278</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.3087573587625172</v>
+        <v>-0.02213865171899132</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4435848347634808</v>
+        <v>0.01417975563177598</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.09339768107431923</v>
+        <v>-0.03581062148903069</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.07148023012745819</v>
+        <v>0.0817485147145196</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1819075574968743</v>
+        <v>0.02395633122549046</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1843606641792332</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1296356571838232</v>
+        <v>0.0906505688722604</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09881011019510794</v>
+        <v>0.3208155612581201</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9861495844875346</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1340128512072695</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.6353538037185822</v>
+        <v>-0.005946824936880146</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.2848556336121717</v>
+        <v>1.029090423147515</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1843606641792332</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2372934536282725</v>
+        <v>0.3106799034324066</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2772771526202035</v>
+        <v>0.03008204884056798</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3332825435193982</v>
+        <v>1.140514035386183</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07088439330789187</v>
+        <v>-0.1021137573160278</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.09736942212280786</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.6707857478267707</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3432015902995453</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02915141269701049</v>
+        <v>0.0817485147145196</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1352163094325023</v>
+        <v>0.02395633122549046</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4301411401713009</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.210556104295444</v>
+        <v>0.0906505688722604</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1645373131427465</v>
+        <v>0.3208155612581201</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9933518005540166</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3866954046840075</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1581811626030833</v>
+        <v>-0.005946824936880146</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.821953741927423</v>
+        <v>1.029090423147515</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4301411401713009</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6780428853085008</v>
+        <v>0.3106799034324066</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01982837738352272</v>
+        <v>0.03008204884056798</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9523223417062872</v>
+        <v>1.140514035386183</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.1021137573160278</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.05401785238151002</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1832745767176298</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1092364586203435</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1946422724391584</v>
+        <v>0.02263986786870054</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1803221063128586</v>
+        <v>-0.01398150135913812</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.01747047985140082</v>
+        <v>0.03714065129439015</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,49 +2650,49 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.02359204792244729</v>
+        <v>0.0817485147145196</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.07703707946457228</v>
+        <v>0.02395633122549046</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2543247912284557</v>
+        <v>0.0906505688722604</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1824361712833101</v>
+        <v>0.3208155612581201</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4816886905342951</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.0212067550577778</v>
+        <v>-0.005946824936880146</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.023869993883996</v>
+        <v>1.029090423147515</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.8838252884816873</v>
+        <v>0.3106799034324066</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.1003724075845553</v>
+        <v>0.03008204884056798</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.241347098573505</v>
+        <v>1.140514035386183</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1388121261286483</v>
+        <v>-0.1021137573160278</v>
       </c>
       <c r="Y7" s="2" t="n">
         <v>0</v>
@@ -2755,49 +2756,49 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.02359204792244729</v>
+        <v>0.0817485147145196</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.07703707946457228</v>
+        <v>0.02395633122549046</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2543247912284557</v>
+        <v>0.0906505688722604</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1824361712833101</v>
+        <v>0.3208155612581201</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4816886905342951</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.0212067550577778</v>
+        <v>-0.005946824936880146</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.023869993883996</v>
+        <v>1.029090423147515</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.8838252884816873</v>
+        <v>0.3106799034324066</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1003724075845553</v>
+        <v>0.03008204884056798</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.241347098573505</v>
+        <v>1.140514035386183</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1388121261286483</v>
+        <v>-0.1021137573160278</v>
       </c>
       <c r="Y8" s="2" t="n">
         <v>0</v>
@@ -2809,13 +2810,13 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.2359164261391125</v>
+        <v>0.02263986786870054</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.3072800600846977</v>
+        <v>-0.01398150135913812</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1030194597174592</v>
+        <v>0.03714065129439015</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,64 +2864,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.1208991842158512</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.03029858250081152</v>
+        <v>-0.03796582501302292</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4315445709455075</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2612308812824861</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1497449313992877</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4249696522996187</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.08590302717126352</v>
+        <v>0.2117597153840098</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9033088877761717</v>
+        <v>-0.03587709265072057</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4315445709455075</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5287902965465798</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1070091958162926</v>
+        <v>-0.2060850325577082</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7426946353838357</v>
+        <v>0.03737143334716829</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0767075613399103</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.09965827919196946</v>
+        <v>-0.06047343460868482</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1094304469125795</v>
+        <v>0.2190089481954183</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1884649251211912</v>
+        <v>-0.2292701650942265</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.2831317115626313</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.1996010640335363</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2969,70 +2974,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.04776515143708671</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.05037268293276886</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4639579318376328</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.2502086263265586</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1733867314306485</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.457757915426841</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.02398477480784122</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9730031102631034</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4639579318376328</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.7561064986545469</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.02576982468306643</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.061963965672205</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.133756362730121</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.02475717599718963</v>
+        <v>-0.02213865171899132</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.04617065973752887</v>
+        <v>0.01417975563177598</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.06779757688149424</v>
+        <v>-0.03581062148903069</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.254832977653748</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.2752967234454667</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02823741309548033</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.2831317115626313</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.02133210379490591</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.0534149946425504</v>
+        <v>-0.09123360655355228</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360385</v>
+        <v>0.2716992530341478</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019929</v>
+        <v>0.1810585772249195</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573141</v>
+        <v>-0.4707583434268607</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3305,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.121721302370637</v>
+        <v>0.717110477150922</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3317,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756414</v>
+        <v>-0.1395291740668931</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3363,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1822704228151848</v>
+        <v>-0.01931799600343886</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1223216195212393</v>
+        <v>0.07913542035525478</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4718154607749649</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1693242986572223</v>
+        <v>0.2544644086576291</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2376559716880013</v>
+        <v>0.1825337474969582</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9636627906976745</v>
+        <v>0.9972268441486412</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4706028507084905</v>
+        <v>-0.4804657787516077</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06627797665555812</v>
+        <v>-0.01834216034240954</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9346458839393986</v>
+        <v>1.020620846046152</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4718154607749649</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.233239118112769</v>
+        <v>0.8876177235064009</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.05256006791162027</v>
+        <v>0.09929893773543874</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.099416687109758</v>
+        <v>1.237769844101154</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1671095976979867</v>
+        <v>-0.1388121261286483</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3457,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.1975871140978549</v>
+        <v>0.2834444878548723</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1368616548924535</v>
+        <v>0.412293078958915</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1847647558521955</v>
+        <v>0.1114874581688012</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118271660599822</v>
+        <v>0.1527921426208967</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9614825581395349</v>
+        <v>0.9584026622296173</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2500855498878848</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07708757922255405</v>
+        <v>0.4169603635659389</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9239869583598836</v>
+        <v>0.5312397610786888</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.239468393809461</v>
+        <v>0.711454536798154</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.05549602170052359</v>
+        <v>-0.003293870969882207</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.104970005642202</v>
+        <v>0.9921128744691625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.0129553196858283</v>
+        <v>0.3087264603862077</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.01013769655160734</v>
+        <v>0.4434360999553419</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.002789345595000992</v>
+        <v>-0.09332566891828586</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3559,58 +3568,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.01472245357751434</v>
+        <v>0.07617044401194351</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.03673057746644792</v>
+        <v>0.1842102126274994</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.08177070849265045</v>
+        <v>-0.184360664179233</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0445963551648392</v>
+        <v>0.1297074769335949</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.04606756670274741</v>
+        <v>0.09885789371414053</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9941860465116279</v>
+        <v>0.9861342207432058</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.04376507628806514</v>
+        <v>-0.1319696276299059</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9259874010041189</v>
+        <v>0.6401399277423194</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.08692010333416339</v>
+        <v>0.2803341235956434</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.08177070849265045</v>
+        <v>-0.184360664179233</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.06116439424586306</v>
+        <v>0.2397843189213968</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4998568412070873</v>
+        <v>-0.2779822059099646</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.0545272645857743</v>
+        <v>0.3343757015990887</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.01866530964473412</v>
+        <v>-0.07088439330789187</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.141717128335758</v>
+        <v>0.09736942212280786</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.8062713881094015</v>
+        <v>0.6707857478267707</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5248317183595569</v>
+        <v>-0.3432015902995452</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3665,67 +3674,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1591911135642186</v>
+        <v>0.03365633972165072</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1004125814229184</v>
+        <v>0.1374279981916635</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4715881184443683</v>
+        <v>-0.4301411401713008</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1917025078547084</v>
+        <v>0.2106727756083452</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2129048142208037</v>
+        <v>0.1646244553931748</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.96875</v>
+        <v>0.9933444259567388</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4703749864436489</v>
+        <v>-0.3852483642619851</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06673692632612682</v>
+        <v>0.1615707647023785</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9341933316505411</v>
+        <v>0.8183569545631199</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4715881184443683</v>
+        <v>-0.4301411401713008</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.188701598099431</v>
+        <v>0.6814210481615666</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.03156884726281239</v>
+        <v>-0.02078458518788628</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.05971206536529</v>
+        <v>0.9502316168477283</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01952117620942473</v>
+        <v>0.05401785238151002</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.0004304221606530323</v>
+        <v>0.18327457671763</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.01994301445470614</v>
+        <v>-0.1092364586203437</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.03206113365920782</v>
+        <v>-0.19462325834654</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.009609852621175308</v>
+        <v>-0.1802376449125536</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.02266912801732957</v>
+        <v>-0.01754851676795055</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -3773,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4071214040372242</v>
+        <v>-0.01931799600343886</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3357711929235401</v>
+        <v>0.07913542035525478</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2593252365148109</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06447408799850961</v>
+        <v>0.2544644086576291</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.159631606047431</v>
+        <v>0.1825337474969582</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9404069767441861</v>
+        <v>0.9972268441486412</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2576247897817361</v>
+        <v>-0.4804657787516077</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4952448046426805</v>
+        <v>-0.01834216034240954</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5116585014471274</v>
+        <v>1.020620846046152</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2593252365148109</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.8954315616540052</v>
+        <v>0.8876177235064009</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.106653847733816</v>
+        <v>0.09929893773543874</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7982656295833975</v>
+        <v>1.237769844101154</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1671095976979867</v>
+        <v>-0.1388121261286483</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.190185745057067</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4023029991978277</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1512634960219724</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3879,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1531374451282819</v>
+        <v>-0.01931799600343886</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.09466587336700072</v>
+        <v>0.07913542035525478</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.465234323249737</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1640840734872686</v>
+        <v>0.2544644086576291</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2270811418593941</v>
+        <v>0.1825337474969582</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9709302325581395</v>
+        <v>0.9972268441486412</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.464006604157876</v>
+        <v>-0.4804657787516077</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.07956371579284527</v>
+        <v>-0.01834216034240954</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9215453371010195</v>
+        <v>1.020620846046152</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.465234323249737</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.151402338300333</v>
+        <v>0.8876177235064009</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.01398913038038163</v>
+        <v>0.09929893773543874</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.026460258771023</v>
+        <v>1.237769844101154</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1671095976979867</v>
+        <v>-0.1388121261286483</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.02464155164901483</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.01245992079753777</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03664488014234379</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.03711602141198478</v>
+        <v>-0.2358983865085925</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.002298918507702474</v>
+        <v>-0.3072086807092197</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.03932453601603314</v>
+        <v>0.1029318529476213</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -3987,58 +3996,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2887047575590527</v>
+        <v>-0.1170510769562687</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2233590409412598</v>
+        <v>-0.02840935865245309</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1671095976979869</v>
+        <v>-0.4315445709455076</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.05647491251919048</v>
+        <v>0.2613574573206263</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1373699969938382</v>
+        <v>0.1498238098316257</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9972268441486412</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.04376507628806503</v>
+        <v>-0.4236129167340174</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.9259874010041191</v>
+        <v>0.08908109576655754</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.08692010333416317</v>
+        <v>0.8998521696935826</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.08177070849265033</v>
+        <v>-0.4315445709455076</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3476863536384223</v>
+        <v>0.5318679905883337</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3648146190865745</v>
+        <v>-0.1078803542506758</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3099578771515034</v>
+        <v>0.7416820804256602</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1671095976979869</v>
+        <v>-0.0767075613399103</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.09002537210601091</v>
+        <v>-0.0996582791919699</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.8062713881094017</v>
+        <v>0.1094304469125791</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3965328913021621</v>
+        <v>-0.1884649251211912</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4093,67 +4102,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.08563975458568907</v>
+        <v>-0.04359691297365842</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.03059075493231744</v>
+        <v>0.05241907482871833</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4715881184443683</v>
+        <v>-0.4639579318376328</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1991840001176012</v>
+        <v>0.2503434696659359</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2238330596657762</v>
+        <v>0.1734791458440214</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9781976744186046</v>
+        <v>0.9972268441486412</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4703749864436489</v>
+        <v>-0.456478541000346</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.06673692632612682</v>
+        <v>0.02698162975109897</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9341933316505411</v>
+        <v>0.9696663848322568</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4715881184443683</v>
+        <v>-0.4639579318376328</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1.049827192442788</v>
+        <v>0.7596418157741041</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.03388480374284786</v>
+        <v>0.02476913348857512</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9359073329748592</v>
+        <v>1.059309325380601</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1671095976979866</v>
+        <v>-0.133756362730121</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.08173313513113345</v>
+        <v>-0.02475717599718974</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.0004304221606530323</v>
+        <v>0.0461706597375291</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.08212820749126748</v>
+        <v>-0.06779757688149446</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.09347742489405131</v>
+        <v>-0.2548153846335358</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.009609852621175308</v>
+        <v>-0.2752220484371313</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.0846813475425221</v>
+        <v>0.02815574585235581</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -4399,28 +4408,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.0534149946425504</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702552</v>
+        <v>0.2216991067360385</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962864</v>
+        <v>0.2389480542019929</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573141</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4429,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.121721302370637</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4441,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756414</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4487,49 +4496,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.03061996343987849</v>
+        <v>0.1822704228151848</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.007045166365681865</v>
+        <v>0.1223216195212393</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.05187138456619264</v>
+        <v>0.1693242986572223</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1829382024919134</v>
+        <v>0.2376559716880013</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.903448275862069</v>
+        <v>0.9636627906976745</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4706028507084905</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.03960193338246176</v>
+        <v>0.06627797665555812</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8369690652301233</v>
+        <v>0.9346458839393986</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2321720269664671</v>
+        <v>1.233239118112769</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.03131657028652601</v>
+        <v>0.05256006791162027</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8535519096845917</v>
+        <v>1.099416687109758</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02321227998309094</v>
+        <v>-0.1671095976979867</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4581,58 +4590,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.1975871140978549</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>0.1368616548924535</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.1847647558521955</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.2118271660599822</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9614825581395349</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.07708757922255405</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.9239869583598836</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>1.239468393809461</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>0.05549602170052359</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>1.104970005642202</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01342358529855958</v>
+        <v>0.0129553196858283</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02048272851701971</v>
+        <v>0.01013769655160734</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03322575960188234</v>
+        <v>0.002789345595000992</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4683,58 +4692,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03061996343987738</v>
+        <v>0.01472245357751434</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.007045166365680755</v>
+        <v>-0.03673057746644792</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1652260547018464</v>
+        <v>-0.08177070849265045</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.05187138456619276</v>
+        <v>0.0445963551648392</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1829382024919132</v>
+        <v>0.04606756670274741</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.903448275862069</v>
+        <v>0.9941860465116279</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1635746138652394</v>
+        <v>-0.04376507628806514</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.03960193338246132</v>
+        <v>0.9259874010041189</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8369690652301255</v>
+        <v>0.08692010333416339</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1652260547018464</v>
+        <v>-0.08177070849265045</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2321720269664667</v>
+        <v>0.06116439424586306</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.03131657028652635</v>
+        <v>-0.4998568412070873</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.85355190968459</v>
+        <v>0.0545272645857743</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02321227998309094</v>
+        <v>-0.01866530964473412</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-1.110223024625157e-15</v>
+        <v>-0.141717128335758</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-5.551115123125783e-16</v>
+        <v>0.8062713881094015</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
+        <v>-0.5248317183595569</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4789,67 +4798,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03061996343987849</v>
+        <v>0.1591911135642186</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.007045166365681865</v>
+        <v>0.1004125814229184</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.05187138456619264</v>
+        <v>0.1917025078547084</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1829382024919134</v>
+        <v>0.2129048142208037</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.903448275862069</v>
+        <v>0.96875</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4703749864436489</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.03960193338246176</v>
+        <v>0.06673692632612682</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8369690652301233</v>
+        <v>0.9341933316505411</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2321720269664671</v>
+        <v>1.188701598099431</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.03131657028652601</v>
+        <v>0.03156884726281239</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8535519096845917</v>
+        <v>1.05971206536529</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02321227998309094</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>-0.01952117620942473</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.0004304221606530323</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.01994301445470614</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.01360622968330527</v>
+        <v>-0.03206113365920782</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.02007160723512247</v>
+        <v>-0.009609852621175308</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.03436765090906846</v>
+        <v>-0.02266912801732957</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -4897,58 +4906,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.09208999923243133</v>
+        <v>0.4071214040372242</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1128578814674021</v>
+        <v>0.3357711929235401</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.2593252365148109</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.08209055631520776</v>
+        <v>0.06447408799850961</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1599211641629928</v>
+        <v>0.159631606047431</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9404069767441861</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.2576247897817361</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.03960193338246176</v>
+        <v>0.4952448046426805</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8369690652301233</v>
+        <v>0.5116585014471274</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.2593252365148109</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08546442494189233</v>
+        <v>0.8954315616540052</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1466521078446044</v>
+        <v>-0.106653847733816</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3141994497458717</v>
+        <v>0.7982656295833975</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1671095976979867</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1190642205908212</v>
+        <v>0.190185745057067</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.4023029991978277</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1190642205908212</v>
+        <v>-0.1512634960219724</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5003,67 +5012,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.003551984318951984</v>
+        <v>0.1531374451282819</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.01940364939957429</v>
+        <v>0.09466587336700072</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.465234323249737</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.05741014267468564</v>
+        <v>0.1640840734872686</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1786851521102313</v>
+        <v>0.2270811418593941</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9709302325581395</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.464006604157876</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.03960193338246176</v>
+        <v>0.07956371579284527</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8369690652301233</v>
+        <v>0.9215453371010195</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.465234323249737</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.199810528176944</v>
+        <v>1.151402338300333</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.05675786172314523</v>
+        <v>0.01398913038038163</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7345788384969824</v>
+        <v>1.026460258771023</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0233044746011295</v>
+        <v>-0.1671095976979867</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.02626378304431665</v>
+        <v>-0.02464155164901483</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.01245992079753777</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02626378304431654</v>
+        <v>-0.03664488014234379</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.01301490442546493</v>
+        <v>-0.03711602141198478</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.02007160723512247</v>
+        <v>0.002298918507702474</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.007201243337533247</v>
+        <v>-0.03932453601603314</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5111,58 +5120,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.09208999923243189</v>
+        <v>0.2887047575590527</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1128578814674026</v>
+        <v>0.2233590409412598</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1652260547018467</v>
+        <v>-0.1671095976979869</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.08209055631520813</v>
+        <v>0.05647491251919048</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1599211641629926</v>
+        <v>0.1373699969938382</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1635746138652395</v>
+        <v>-0.04376507628806503</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.0396019333824611</v>
+        <v>0.9259874010041191</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.836969065230126</v>
+        <v>0.08692010333416317</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1652260547018467</v>
+        <v>-0.08177070849265033</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08546442494189233</v>
+        <v>0.3476863536384223</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1466521078446044</v>
+        <v>-0.3648146190865745</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3141994497458717</v>
+        <v>0.3099578771515034</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.1671095976979869</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1190642205908218</v>
+        <v>0.09002537210601091</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>0.8062713881094017</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1190642205908212</v>
+        <v>-0.3965328913021621</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5217,67 +5226,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.003551984318951984</v>
+        <v>0.08563975458568907</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.01940364939957429</v>
+        <v>0.03059075493231744</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.05741014267468564</v>
+        <v>0.1991840001176012</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1786851521102313</v>
+        <v>0.2238330596657762</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9781976744186046</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4703749864436489</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.03960193338246176</v>
+        <v>0.06673692632612682</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.8369690652301233</v>
+        <v>0.9341933316505411</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.199810528176944</v>
+        <v>1.049827192442788</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.05675786172314523</v>
+        <v>-0.03388480374284786</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7345788384969824</v>
+        <v>0.9359073329748592</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.0233044746011295</v>
+        <v>-0.1671095976979866</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.02626378304431665</v>
+        <v>-0.08173313513113345</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0</v>
+        <v>0.0004304221606530323</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.02626378304431654</v>
+        <v>-0.08212820749126748</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.01301490442546493</v>
+        <v>-0.09347742489405131</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.02007160723512247</v>
+        <v>-0.009609852621175308</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.007201243337533247</v>
+        <v>-0.0846813475425221</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5523,28 +5532,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.01891210187562642</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570336</v>
+        <v>0.08099293800751969</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886579</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5553,10 +5562,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5565,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886031</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5611,49 +5620,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.04515891089417345</v>
+        <v>0.03014589372818866</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.04797439533710812</v>
+        <v>0.0110252806222273</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1195047161892575</v>
+        <v>0.05169621954656301</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4584419203783911</v>
+        <v>0.1823084026644021</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.01649499533326504</v>
+        <v>0.0437107207679579</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.824028865917714</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4972066941042887</v>
+        <v>0.2321720269664671</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.03200736127876636</v>
+        <v>-0.03131657028652601</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9094475381374805</v>
+        <v>0.8535519096845917</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.06227097997115527</v>
+        <v>-0.02321227998309094</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5705,58 +5714,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.01712918805183983</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.001749821030199383</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04617799198161064</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.167065999353103</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03961745603147049</v>
+        <v>-0.01263578853791303</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.01673316320564022</v>
+        <v>0.02129760000172332</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05542321355924296</v>
+        <v>-0.03322575960188234</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5807,58 +5816,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.04515891089417412</v>
+        <v>0.03014589372818777</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.04797439533710757</v>
+        <v>0.01102528062222641</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3019274392708715</v>
+        <v>-0.1652260547018465</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1195047161892574</v>
+        <v>0.05169621954656305</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4584419203783909</v>
+        <v>0.1823084026644019</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3019274392708715</v>
+        <v>-0.1639593569865849</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.01649499533326493</v>
+        <v>0.04371072076795723</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.8240288659177162</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3019274392708715</v>
+        <v>-0.1652260547018465</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.4972066941042894</v>
+        <v>0.2321720269664667</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.03200736127876591</v>
+        <v>-0.03131657028652635</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9094475381374817</v>
+        <v>0.85355190968459</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06227097997115505</v>
+        <v>-0.02321227998309094</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-5.551115123125783e-16</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5913,49 +5922,49 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.04515891089417345</v>
+        <v>0.03014589372818866</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04797439533710812</v>
+        <v>0.0110252806222273</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1195047161892575</v>
+        <v>0.05169621954656301</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4584419203783911</v>
+        <v>0.1823084026644021</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.01649499533326504</v>
+        <v>0.0437107207679579</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.824028865917714</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4972066941042887</v>
+        <v>0.2321720269664671</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.03200736127876636</v>
+        <v>-0.03131657028652601</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9094475381374805</v>
+        <v>0.8535519096845917</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.06227097997115527</v>
+        <v>-0.02321227998309094</v>
       </c>
       <c r="Y6" s="2" t="n">
         <v>0</v>
@@ -5967,13 +5976,13 @@
         <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.04125174523452046</v>
+        <v>0.01279749497827343</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.01645777261054659</v>
+        <v>-0.02085347111526292</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.05867518062568755</v>
+        <v>0.03436765090906846</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -6021,58 +6030,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.04515891089417345</v>
+        <v>-0.09250762420339298</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.04797439533710812</v>
+        <v>-0.1093516564126744</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1195047161892575</v>
+        <v>0.08181185189601717</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4584419203783911</v>
+        <v>0.1593689880128749</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.01649499533326504</v>
+        <v>0.0437107207679579</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.824028865917714</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4972066941042887</v>
+        <v>0.08546442494189233</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.03200736127876636</v>
+        <v>-0.1466521078446044</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9094475381374805</v>
+        <v>0.3141994497458717</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.06227097997115527</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1190642205908211</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1190642205908212</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6127,67 +6136,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.04515891089417345</v>
+        <v>0.003090365471317913</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.04797439533710812</v>
+        <v>-0.01552806800035411</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1195047161892575</v>
+        <v>0.05721595479114579</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4584419203783911</v>
+        <v>0.1780690682775942</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.01649499533326504</v>
+        <v>0.0437107207679579</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.824028865917714</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4972066941042887</v>
+        <v>0.199810528176944</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.03200736127876636</v>
+        <v>-0.05675786172314523</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9094475381374805</v>
+        <v>0.7345788384969824</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.06227097997115527</v>
+        <v>-0.0233044746011295</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>-0.02626378304431654</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
+        <v>-0.02626378304431654</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.04125174523452046</v>
+        <v>-0.0138023986976632</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01645777261054659</v>
+        <v>-0.02085347111526292</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.05867518062568755</v>
+        <v>0.007201243337533247</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -6235,58 +6244,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.04515891089417456</v>
+        <v>-0.09250762420339353</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.04797439533710712</v>
+        <v>-0.109351656412675</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018466</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1195047161892573</v>
+        <v>0.08181185189601732</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.458441920378391</v>
+        <v>0.1593689880128747</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.163959356986585</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.01649499533326504</v>
+        <v>0.04371072076795723</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.8240288659177167</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018466</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4972066941042901</v>
+        <v>0.08546442494189233</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.03200736127876547</v>
+        <v>-0.1466521078446044</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.9094475381374829</v>
+        <v>0.3141994497458717</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.06227097997115527</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>1.110223024625157e-15</v>
+        <v>-0.1190642205908217</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>-6.661338147750939e-16</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>-0.1190642205908212</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6341,67 +6350,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.04515891089417345</v>
+        <v>0.003090365471317913</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.04797439533710812</v>
+        <v>-0.01552806800035411</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1195047161892575</v>
+        <v>0.05721595479114579</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4584419203783911</v>
+        <v>0.1780690682775942</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.01649499533326504</v>
+        <v>0.0437107207679579</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.824028865917714</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4972066941042887</v>
+        <v>0.199810528176944</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.03200736127876636</v>
+        <v>-0.05675786172314523</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9094475381374805</v>
+        <v>0.7345788384969824</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.06227097997115527</v>
+        <v>-0.0233044746011295</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
+        <v>-0.02626378304431654</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0</v>
+        <v>-0.02626378304431654</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.04125174523452046</v>
+        <v>-0.0138023986976632</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01645777261054659</v>
+        <v>-0.02085347111526292</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.05867518062568755</v>
+        <v>0.007201243337533247</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6647,28 +6656,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363057</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752893</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2405796270435321</v>
+        <v>0.4518304992174231</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450099</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6677,10 +6686,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682997</v>
+        <v>0.5657770181230004</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6689,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174769</v>
+        <v>-0.05185156587886031</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6735,49 +6744,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.265288122701582</v>
+        <v>0.05462537085906805</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1925238525356017</v>
+        <v>-0.05104786499468505</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1660049019432621</v>
+        <v>0.1176077422857334</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2482386617226885</v>
+        <v>0.4511654067224259</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3240432642895691</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02059198849579269</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.045869944982081</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.8718477912225604</v>
+        <v>0.5107675479430458</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.2175965874570334</v>
+        <v>-0.03513237807379377</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.622555509664736</v>
+        <v>0.9027718192540731</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.11030602040881</v>
+        <v>-0.06227097997115527</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6829,58 +6838,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.09480060127513035</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.03184073837926271</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1155318330023982</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1720647483703307</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4372788934221374</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06508110111248899</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.813799478447114</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1347420546890419</v>
+        <v>-0.04545468390951546</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1268732750341672</v>
+        <v>0.01673316320564022</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2321603817565705</v>
+        <v>-0.06116437366819527</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6931,68 +6940,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1263488884464483</v>
+        <v>0.05462537085906871</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.06157474463715018</v>
+        <v>-0.0510478649946845</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.01186277237784117</v>
+        <v>-0.3019274392708715</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0007600484582676122</v>
+        <v>0.1176077422857332</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.02250233551180395</v>
+        <v>0.4511654067224257</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.01169590643274854</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3019274392708715</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.01649499533326493</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3019274392708715</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1137592019472806</v>
+        <v>0.5107675479430465</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2755236777803596</v>
+        <v>-0.03513237807379332</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2117119774264644</v>
+        <v>0.9027718192540743</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.01186277237784128</v>
+        <v>-0.06227097997115505</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1098083762601654</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.4961072570703728</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.4049947826047059</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.3582787676295329</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.2634396529978946</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7041,74 +7046,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1204395516645749</v>
+        <v>0.05462537085906805</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.05600524237231941</v>
+        <v>-0.05104786499468505</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1155339419722308</v>
+        <v>0.1176077422857334</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1731326282669589</v>
+        <v>0.4511654067224259</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.470938285097048</v>
+        <v>0.5107675479430458</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.04318639331016105</v>
+        <v>-0.03513237807379377</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8764414120092855</v>
+        <v>0.9027718192540731</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.06227097997115527</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1144787249940618</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1268732750341661</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2141784754110089</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.0234188311182717</v>
+        <v>0.04761919957418415</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.01645777261054659</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.02341883111827259</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.3582787676295329</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.0883258250595057</v>
-      </c>
+        <v>0.0651491826180215</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7153,58 +7154,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.2130697391495751</v>
+        <v>0.05462537085906805</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2583245748466383</v>
+        <v>-0.05104786499468505</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2434135188916345</v>
+        <v>0.1176077422857334</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2042853685498822</v>
+        <v>0.4511654067224259</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3240432642895691</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02059198849579269</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.045869944982081</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1641725265498846</v>
+        <v>0.5107675479430458</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.242730898214451</v>
+        <v>-0.03513237807379377</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3055338789303598</v>
+        <v>0.9027718192540731</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.08674868744033093</v>
+        <v>-0.06227097997115527</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.3780623980171334</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3780623980171335</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7259,67 +7260,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.04457206278515979</v>
+        <v>0.05462537085906805</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.09951687361542982</v>
+        <v>-0.05104786499468505</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2018601969694581</v>
+        <v>0.1176077422857334</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.221621552835279</v>
+        <v>0.4511654067224259</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3240432642895691</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02059198849579269</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.045869944982081</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4134453978192627</v>
+        <v>0.5107675479430458</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08058427559564441</v>
+        <v>-0.03513237807379377</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7694440645843484</v>
+        <v>0.9027718192540731</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08900367010415333</v>
+        <v>-0.06227097997115527</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.244892985184389</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.244892985184389</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1273041537408371</v>
+        <v>0.04761919957418415</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.1125887691589105</v>
+        <v>-0.01645777261054659</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.01658237361722303</v>
+        <v>0.0651491826180215</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -7367,58 +7368,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1263488884464483</v>
+        <v>0.0546253708590696</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.06157474463715018</v>
+        <v>-0.05104786499468372</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.01186277237784117</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0007600484582676122</v>
+        <v>0.1176077422857332</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.02250233551180389</v>
+        <v>0.4511654067224259</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.01169590643274854</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1137592019472806</v>
+        <v>0.5107675479430476</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2755236777803596</v>
+        <v>-0.03513237807379255</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2117119774264644</v>
+        <v>0.9027718192540763</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01186277237784128</v>
+        <v>-0.06227097997115527</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1098083762601654</v>
+        <v>1.554312234475219e-15</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4961072570703728</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4049947826047059</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -7473,67 +7474,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1204395516645749</v>
+        <v>0.05462537085906805</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.05600524237231941</v>
+        <v>-0.05104786499468505</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1155339419722308</v>
+        <v>0.1176077422857334</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1731326282669589</v>
+        <v>0.4511654067224259</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.470938285097048</v>
+        <v>0.5107675479430458</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04318639331016105</v>
+        <v>-0.03513237807379377</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.8764414120092855</v>
+        <v>0.9027718192540731</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.06227097997115527</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.1144787249940618</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1268732750341661</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.2141784754110089</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.0234188311182717</v>
+        <v>0.04761919957418415</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.01645777261054659</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02341883111827259</v>
+        <v>0.0651491826180215</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -7779,28 +7780,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974677</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.103821015825279</v>
+        <v>0.1799741913752893</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005</v>
+        <v>0.2405796270435321</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450099</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7809,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922785</v>
+        <v>0.5373300241682997</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7821,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174769</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7867,49 +7868,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.02466362643383457</v>
+        <v>0.265288122701582</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.02232108134351685</v>
+        <v>0.1925238525356017</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.09228250964986333</v>
+        <v>0.1660049019432621</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2759947934484516</v>
+        <v>0.2482386617226885</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.3240432642895691</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.04680968554454545</v>
+        <v>-0.02059198849579269</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8380254332546916</v>
+        <v>1.045869944982081</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2009850468985936</v>
+        <v>0.8718477912225604</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.06603947961381429</v>
+        <v>0.2175965874570334</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.702976994072228</v>
+        <v>1.622555509664736</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.05694989141396378</v>
+        <v>-0.11030602040881</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7961,58 +7962,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.02335558522365555</v>
+        <v>0.09480060127513035</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.02100989850384682</v>
+        <v>0.03184073837926271</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07028481312061448</v>
+        <v>0.1155318330023982</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1720647483703307</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6940712220239806</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4372788934221374</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.06508110111248899</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.813799478447114</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.001341118044635659</v>
+        <v>-0.1347420546890419</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03974161746077343</v>
+        <v>0.1268732750341672</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03693273287446019</v>
+        <v>-0.2321603817565705</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8063,67 +8064,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1263488884464483</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.06157474463715018</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.01186277237784117</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.0007600484582676122</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.02250233551180395</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.01169590643274854</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1137592019472806</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2755236777803596</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2117119774264644</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.01186277237784128</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.04056066239060607</v>
+        <v>-0.1098083762601654</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2383736081761483</v>
+        <v>0.4961072570703728</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1597360800323235</v>
+        <v>-0.4049947826047059</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.03585765398568408</v>
+        <v>0.3582787676295329</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.02974365309812033</v>
+        <v>-0.2634396529978946</v>
       </c>
     </row>
     <row r="6">
@@ -8173,73 +8174,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>0.1204395516645749</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>0.05600524237231941</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.1155339419722308</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1731326282669589</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9434697855750487</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.470938285097048</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.04318639331016105</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.8764414120092855</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.001341118044635659</v>
+        <v>-0.1144787249940618</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03974161746077365</v>
+        <v>0.1268732750341661</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.03693273287446019</v>
+        <v>-0.2141784754110089</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.0234188311182717</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>0.02341883111827259</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.03585765398568408</v>
+        <v>0.3582787676295329</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.02898025511974711</v>
+        <v>-0.0883258250595057</v>
       </c>
     </row>
     <row r="7">
@@ -8285,68 +8286,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.2130697391495751</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.2583245748466383</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.2434135188916345</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2042853685498822</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.3240432642895691</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>-0.02059198849579269</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>1.045869944982081</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1641725265498846</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.242730898214451</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.3055338789303598</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.08674868744033093</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.04056066239060607</v>
+        <v>-0.3780623980171334</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2383736081761483</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1597360800323235</v>
+        <v>-0.3780623980171335</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.02974365309812033</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8395,19 +8392,19 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>-0.04457206278515979</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>-0.09951687361542982</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.2018601969694581</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.221621552835279</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -8416,53 +8413,49 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.3240432642895691</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>-0.02059198849579269</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>1.045869944982081</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4134453978192627</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.08058427559564441</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.7694440645843484</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08900367010415333</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.001341118044635659</v>
+        <v>-0.244892985184389</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03974161746077365</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03693273287446019</v>
+        <v>-0.244892985184389</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.1273041537408371</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.1125887691589105</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0.02898025511974711</v>
-      </c>
+        <v>-0.01658237361722303</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8507,68 +8500,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1263488884464483</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.06157474463715018</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.01186277237784117</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.0007600484582676122</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.02250233551180389</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>0.01169590643274854</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1137592019472806</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2755236777803596</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2117119774264644</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.01186277237784128</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.04056066239060607</v>
+        <v>-0.1098083762601654</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.2383736081761483</v>
+        <v>0.4961072570703728</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1597360800323235</v>
+        <v>-0.4049947826047059</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.02974365309812033</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8617,74 +8606,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>0.1204395516645749</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>0.05600524237231941</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.1155339419722308</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1731326282669589</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9434697855750487</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.470938285097048</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.04318639331016105</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.8764414120092855</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.001341118044635659</v>
+        <v>-0.1144787249940618</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.03974161746077365</v>
+        <v>0.1268732750341661</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03693273287446019</v>
+        <v>-0.2141784754110089</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.0234188311182717</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.02898025511974711</v>
-      </c>
+        <v>0.02341883111827259</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8697,7 +8682,1155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947871</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490124</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.02221658291291773</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.02700858475410772</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.09179827266736014</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.274462303017576</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.04680968554454545</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.8380254332546916</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.203998225487418</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.07051737418750892</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.6907177825656089</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.05694989141396378</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.02027479846139824</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.02507631676042987</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.06992591782126945</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2355679791479366</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6940712220239806</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1602779293212004</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1042692974226319</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.5426851908659128</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.001985904462671551</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.03974161746077343</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.03631259186326308</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.03813050191644218</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.2383736081761483</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1616984607372408</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.02974365309812033</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.001985904462671773</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.03974161746077365</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.03631259186326286</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.02898025511974711</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.03813050191644218</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.2383736081761483</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1616984607372408</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.02974365309812033</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.001985904462671773</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.03974161746077365</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.03631259186326286</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.02898025511974711</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>0.03813050191644218</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.2383736081761483</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1616984607372408</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.02974365309812033</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>0.001985904462671773</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.03974161746077365</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.03631259186326286</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.02898025511974711</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8803,12 +9936,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -8817,10 +9946,10 @@
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8851,10 +9980,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -8864,7 +9993,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -8897,8 +10026,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -8907,10 +10040,10 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8983,24 +10116,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9031,21 +10160,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.9766081871345029</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9062,30 +10193,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -9115,15 +10248,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -9132,10 +10261,10 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9162,7 +10291,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -9171,16 +10300,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9207,11 +10334,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -9220,10 +10351,10 @@
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9250,7 +10381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -9262,13 +10393,13 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9295,22 +10426,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -9330,37 +10459,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="2" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9377,37 +10504,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9434,25 +10559,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9479,11 +10606,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -9492,10 +10623,10 @@
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9522,14 +10653,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -9539,7 +10670,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -9569,30 +10700,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
